--- a/sumprod_final_ready_for_upload.xlsx
+++ b/sumprod_final_ready_for_upload.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P58"/>
+  <dimension ref="A1:P63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,12 +562,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$$\cos(5x) + \cos(2x)$$</t>
+          <t>$$cos(2x) + cos(5x)$$</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>algebra</t>
+          <t>algebraic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -595,12 +595,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Recall the product-to-sum formula for cosine.</t>
+          <t>Recall Product-to-Sum Formula</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>The product-to-sum formula for two cosines is $2\cos A \cos B = \cos(A-B) + \cos(A+B)$.</t>
+          <t>The product-to-sum formula for $$2cosAcosB$$ is $$cos(A-B) + cos(A+B)$$.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -633,22 +633,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Identify A and B.</t>
+          <t>Identify A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>In the expression $2cos(\frac{7x}{2})cos\frac{3x}{2}$, what are A and B?</t>
+          <t>What is A in the expression $$2cos(\frac{7x}{2})cos\frac{3x}{2}$$?</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>$$A = \frac{7x}{2}, B = \frac{3x}{2}$$</t>
+          <t>$$7x/2$$</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>algebra</t>
+          <t>algebraic</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -683,12 +683,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Apply the formula.</t>
+          <t>Identify B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Substitute the values of A and B into the formula $2\cos A \cos B = \cos(A-B) + \cos(A+B)$.</t>
+          <t>What is B in the expression $$2cos(\frac{7x}{2})cos\frac{3x}{2}$$?</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -725,22 +725,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Calculate A-B and A+B.</t>
+          <t>Identify B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>What are the values of $A-B$ and $A+B$?</t>
+          <t>What is B in the expression $$2cos(\frac{7x}{2})cos\frac{3x}{2}$$?</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>$$A-B = 2x, A+B = 5x$$</t>
+          <t>$$3x/2$$</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>algebra</t>
+          <t>algebraic</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -763,14 +763,38 @@
       <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>sumprod1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>hint</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Calculate A-B and A+B</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Now calculate $$A-B$$ and $$A+B$$ using the identified values.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>h3</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -783,63 +807,59 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>sumprod2</t>
+          <t>sumprod1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>problem</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Writing the Product as a Sum Containing only Sine or Cosine</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+          <t>Calculate A-B</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>What is $$A - B$$?</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>$$2x$$</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>algebraic</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>s3</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>h3</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>https://openstax.org/books/precalculus-2e/pages/7-4-sum-to-product-and-product-to-sum-formulas</t>
-        </is>
-      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>sumprod2</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>step</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Express the following product as a sum containing only sine or cosine and no products: $$sin(4θ)cos(2θ).$$</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>$$\frac{1}{2}(\sin(6\theta) + \sin(2\theta))$$</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>algebra</t>
-        </is>
-      </c>
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -860,31 +880,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>problem</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Recall the product-to-sum formula for sine and cosine.</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>The product-to-sum formula for sine and cosine is $\sin A \cos B = \frac{1}{2}[\sin(A+B) + \sin(A-B)]$.</t>
-        </is>
-      </c>
+          <t>Writing the Product as a Sum Containing only Sine or Cosine</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://openstax.org/books/precalculus-2e/pages/7-4-sum-to-product-and-product-to-sum-formulas</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -898,39 +914,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>step</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Identify A and B.</t>
+          <t>Express the following product as a sum containing only sine or cosine and no products: $$sin(4θ)cos(2θ).$$</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>In the expression $sin(4θ)cos(2θ)$, what are A and B?</t>
+          <t>$$\frac{1}{2}[sin(6θ) + sin(2θ)]$$</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>$$A = 4\theta, B = 2\theta$$</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>algebra</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>s1</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
+          <t>algebraic</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
@@ -953,26 +957,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Apply the formula.</t>
+          <t>Recall Product-to-Sum Formula</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Substitute the values of A and B into the formula $\sin A \cos B = \frac{1}{2}[\sin(A+B) + \sin(A-B)]$.</t>
+          <t>The product-to-sum formula for $$sinAcosB$$ is $$\frac{1}{2}[sin(A+B) + sin(A-B)]$$.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>h2</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
           <t>h1</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
@@ -995,32 +995,32 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Calculate A+B and A-B.</t>
+          <t>Identify A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>What are the values of $A+B$ and $A-B$?</t>
+          <t>What is A in the expression $$sin(4θ)cos(2θ)$$?</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>$$A+B = 6\theta, A-B = 2\theta$$</t>
+          <t>$$4θ$$</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>algebra</t>
+          <t>algebraic</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>s2</t>
+          <t>s1</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>h2</t>
+          <t>h1</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1033,14 +1033,38 @@
       <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>sumprod2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>hint</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Identify B</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>What is B in the expression $$sin(4θ)cos(2θ)$$?</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
@@ -1053,32 +1077,48 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>sumprod3</t>
+          <t>sumprod2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>problem</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Express the Product as a Sum or Difference</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+          <t>Identify B</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>What is B in the expression $$sin(4θ)cos(2θ)$$?</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>$$2θ$$</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>algebraic</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>s2</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>https://openstax.org/books/precalculus-2e/pages/7-4-sum-to-product-and-product-to-sum-formulas</t>
-        </is>
-      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
@@ -1087,32 +1127,36 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>sumprod3</t>
+          <t>sumprod2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>step</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Write $$cos(3θ)cos(5θ)$$ as a sum or difference.</t>
+          <t>Calculate A+B and A-B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>$$\frac{1}{2}(\cos(2\theta) + \cos(8\theta))$$</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>algebra</t>
-        </is>
-      </c>
+          <t>Now calculate $$A+B$$ and $$A-B$$ using the identified values.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>h3</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -1125,32 +1169,44 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>sumprod3</t>
+          <t>sumprod2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Recall the product-to-sum formula for cosine.</t>
+          <t>Calculate A+B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>The product-to-sum formula for two cosines is $\cos A \cos B = \frac{1}{2}[\cos(A-B) + \cos(A+B)]$.</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
+          <t>What is $$A + B$$?</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>$$6θ$$</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>algebraic</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>h1</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>s3</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>h3</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
@@ -1161,46 +1217,14 @@
       <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>sumprod3</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>scaffold</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Identify A and B.</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>In the expression $cos(3θ)cos(5θ)$, what are A and B?</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>$$A = 3\theta, B = 5\theta$$</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>algebra</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>s1</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
@@ -1218,35 +1242,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>problem</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Apply the formula.</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Substitute the values of A and B into the formula $\cos A \cos B = \frac{1}{2}[\cos(A-B) + \cos(A+B)]$.</t>
-        </is>
-      </c>
+          <t>Express the Product as a Sum or Difference</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://openstax.org/books/precalculus-2e/pages/7-4-sum-to-product-and-product-to-sum-formulas</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
@@ -1260,39 +1276,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>step</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Calculate A-B and A+B.</t>
+          <t>Write $$cos(3θ)cos(5θ)$$ as a sum or difference.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>What are the values of $A-B$ and $A+B$? Remember $\cos(-x) = \cos(x)$.</t>
+          <t>$$\frac{1}{2}[cos(2θ) + cos(8θ)]$$</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>$$A-B = -2\theta \implies \cos(2\theta), A+B = 8\theta$$</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>algebra</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>s2</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
+          <t>algebraic</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
@@ -1303,13 +1307,33 @@
       <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>sumprod3</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>hint</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Recall Product-to-Sum Formula</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>The product-to-sum formula for $$cosAcosB$$ is $$\frac{1}{2}[cos(A-B) + cos(A+B)]$$.</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
@@ -1323,32 +1347,48 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>sumprod4</t>
+          <t>sumprod3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>problem</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Writing the Difference of Sines as a Product</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+          <t>Identify A</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>What is A in the expression $$cos(3θ)cos(5θ)$$?</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>$$3θ$$</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>algebraic</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>https://openstax.org/books/precalculus-2e/pages/7-4-sum-to-product-and-product-to-sum-formulas</t>
-        </is>
-      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
@@ -1357,32 +1397,36 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>sumprod4</t>
+          <t>sumprod3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>step</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Write the following difference of sines expression as a product: $$sin(4θ)−sin(2θ).$$</t>
+          <t>Identify B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>$$2cos(3θ)sin(θ)$$</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>algebra</t>
-        </is>
-      </c>
+          <t>What is B in the expression $$cos(3θ)cos(5θ)$$?</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
@@ -1395,32 +1439,44 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>sumprod4</t>
+          <t>sumprod3</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Recall the difference-to-product formula for sines</t>
+          <t>Identify B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Recall the sum-to-product formula for the difference of sines: $$\sin A - \sin B = 2 \cos\left(\frac{A+B}{2}\right) \sin\left(\frac{A-B}{2}\right)$$</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
+          <t>What is B in the expression $$cos(3θ)cos(5θ)$$?</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>$$5θ$$</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>h1</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+          <t>algebraic</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>s2</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
@@ -1433,42 +1489,34 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>sumprod4</t>
+          <t>sumprod3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Identify A and B</t>
+          <t>Calculate A-B and A+B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>In the expression $$\sin(4θ)−\sin(2θ)$$, what are A and B?</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>$$A=4θ, B=2θ$$</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>algebra</t>
-        </is>
-      </c>
+          <t>Now calculate $$A-B$$ and $$A+B$$ using the identified values. Remember $$cos(-x) = cos(x)$$.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>s1</t>
+          <t>h3</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>h1</t>
+          <t>h2</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -1483,36 +1531,44 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>sumprod4</t>
+          <t>sumprod3</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Calculate the sum and difference of A and B</t>
+          <t>Calculate A-B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Find $$\frac{A+B}{2}$$ and $$\frac{A-B}{2}$$.</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
+          <t>What is $$A - B$$?</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>$$-2θ$$</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>h2</t>
+          <t>algebraic</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>h1</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>s3</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>h3</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
@@ -1530,43 +1586,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>problem</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Calculate the average and half-difference</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>What are $$\frac{4θ+2θ}{2}$$ and $$\frac{4θ-2θ}{2}$$?</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>$$3θ, θ$$</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>algebra</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>s2</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
+          <t>Writing the Difference of Sines as a Product</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://openstax.org/books/precalculus-2e/pages/7-4-sum-to-product-and-product-to-sum-formulas</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
@@ -1580,30 +1620,26 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>step</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Substitute into the formula</t>
+          <t>Write the following difference of sines expression as a product: $$sin(4θ)−sin(2θ).$$</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Substitute the values of A, B, $$\frac{A+B}{2}$$, and $$\frac{A-B}{2}$$ into the difference-to-product formula.</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
+          <t>$$2cos(3θ)sin(θ)$$</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>algebraic</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
@@ -1622,39 +1658,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Apply the formula</t>
+          <t>Recall the difference-to-product formula for sines</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>What is the resulting product expression?</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>$$2cos(3θ)sin(θ)$$</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>algebra</t>
-        </is>
-      </c>
+          <t>The difference of sines formula is $$sin(A)−sin(B)=2cos\left(\frac{A+B}{2}\right)sin\left(\frac{A−B}{2}\right).$$</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>s3</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
+          <t>h1</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
@@ -1667,32 +1691,48 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>sumprod5</t>
+          <t>sumprod4</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>problem</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Evaluating Using the Sum-to-Product Formula</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+          <t>Identify A and B</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>In the expression $$sin(4θ)−sin(2θ)$$, what are A and B?</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>A=4θ, B=2θ</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>algebraic</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>https://openstax.org/books/precalculus-2e/pages/7-4-sum-to-product-and-product-to-sum-formulas</t>
-        </is>
-      </c>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
@@ -1701,32 +1741,36 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>sumprod5</t>
+          <t>sumprod4</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>step</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Evaluate $$cos(15^{∘})−cos(75^{∘}).$$</t>
+          <t>Calculate the sum and difference of angles</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>$$\frac{\sqrt{6}}{2}$$</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
+          <t>Find the values for $$\frac{A+B}{2}$$ and $$\frac{A−B}{2}$$.</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
@@ -1739,32 +1783,44 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>sumprod5</t>
+          <t>sumprod4</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Recall the difference-to-product formula for cosines</t>
+          <t>Calculate (A+B)/2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Recall the sum-to-product formula for the difference of cosines: $$\cos A - \cos B = -2 \sin\left(\frac{A+B}{2}\right) \sin\left(\frac{A-B}{2}\right)$$</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
+          <t>What is the value of $$\frac{4θ+2θ}{2}$$?</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>$$3θ$$</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>h1</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+          <t>algebraic</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>s2</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
@@ -1777,7 +1833,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>sumprod5</t>
+          <t>sumprod4</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1787,32 +1843,32 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Identify A and B</t>
+          <t>Calculate (A-B)/2</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>In the expression $$\cos(15^{∘})−\cos(75^{∘})$$, what are A and B?</t>
+          <t>What is the value of $$\frac{4θ−2θ}{2}$$?</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>$$A=15^{∘}, B=75^{∘}$$</t>
+          <t>$$θ$$</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>algebra</t>
+          <t>algebraic</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>s1</t>
+          <t>s3</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>h1</t>
+          <t>h2</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -1832,35 +1888,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>problem</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Calculate the sum and difference of A and B</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Find $$\frac{A+B}{2}$$ and $$\frac{A-B}{2}$$.</t>
-        </is>
-      </c>
+          <t>Evaluating Using the Sum-to-Product Formula</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>https://openstax.org/books/precalculus-2e/pages/7-4-sum-to-product-and-product-to-sum-formulas</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
@@ -1874,39 +1922,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>step</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Calculate the average and half-difference</t>
+          <t>Evaluate $$cos(15^{∘})−cos(75^{∘}).$$</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>What are $$\frac{15^{∘}+75^{∘}}{2}$$ and $$\frac{15^{∘}-75^{∘}}{2}$$?</t>
+          <t>$$\frac{\sqrt{2}}{2}$$</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>$$45^{∘}, -30^{∘}$$</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>algebra</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>s2</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
@@ -1929,23 +1965,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Substitute and evaluate</t>
+          <t>Recall the difference-to-product formula for cosines</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Substitute the values into the formula and evaluate the sine functions.</t>
+          <t>The difference of cosines formula is $$cos(A)−cos(B)=−2sin\left(\frac{A+B}{2}\right)sin\left(\frac{A−B}{2}\right).$$</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>h2</t>
+          <t>h1</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
@@ -1971,32 +2003,32 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Evaluate the expression</t>
+          <t>Identify A and B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>What is $$-2 \sin(45^{∘}) \sin(-30^{∘})$$?</t>
+          <t>In the expression $$cos(15^{∘})−cos(75^{∘})$$, what are A and B?</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>$$\frac{\sqrt{6}}{2}$$</t>
+          <t>A=15^{∘}, B=75^{∘}</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>algebraic</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>s3</t>
+          <t>s1</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>h3</t>
+          <t>h1</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -2011,32 +2043,40 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>sumprod6</t>
+          <t>sumprod5</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>problem</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Proving an Identity</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
+          <t>Calculate the sum and difference of angles</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Find the values for $$\frac{A+B}{2}$$ and $$\frac{A−B}{2}$$.</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>https://openstax.org/books/precalculus-2e/pages/7-4-sum-to-product-and-product-to-sum-formulas</t>
-        </is>
-      </c>
+      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
@@ -2045,32 +2085,44 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>sumprod6</t>
+          <t>sumprod5</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>step</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Evaluate the expression $$\frac{cos(4t)−cos(2t)}{sin(4t)+sin(2t)}$$</t>
+          <t>Calculate (A+B)/2</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>$$-tant$$</t>
+          <t>What is the value of $$\frac{15^{∘}+75^{∘}}{2}$$?</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>algebra</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+          <t>$$45^{∘}$$</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>s2</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
@@ -2083,28 +2135,44 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>sumprod6</t>
+          <t>sumprod5</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Apply sum-to-product formulas</t>
+          <t>Calculate (A-B)/2</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Use the sum-to-product formulas for the numerator and the denominator.</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+          <t>What is the value of $$\frac{15^{∘}−75^{∘}}{2}$$?</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>$$-30^{∘}$$</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>s3</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
@@ -2117,16 +2185,36 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>*   $$\cos A - \cos B = -2 \sin\left(\frac{A+B}{2}\right) \sin\left(\frac{A-B}{2}\right)$$</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
+          <t>sumprod5</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>hint</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Evaluate sine values</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Recall the values of $$sin(45^{∘})$$ and $$sin(−30^{∘})$$.</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>h3</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
@@ -2139,20 +2227,44 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>*   $$\sin A + \sin B = 2 \sin\left(\frac{A+B}{2}\right) \cos\left(\frac{A-B}{2}\right)$$</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
+          <t>sumprod5</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>scaffold</t>
+        </is>
+      </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>h1</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+          <t>Value of sin(45°)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>What is $$sin(45^{∘})$$?</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>$$\frac{\sqrt{2}}{2}$$</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>s4</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>h3</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
@@ -2165,7 +2277,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>sumprod6</t>
+          <t>sumprod5</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2175,32 +2287,32 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Apply to numerator</t>
+          <t>Value of sin(-30°)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>What is $$\cos(4t)−\cos(2t)$$ as a product?</t>
+          <t>What is $$sin(−30^{∘})$$?</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>$$-2\sin(3t)\sin(t)$$</t>
+          <t>$$-\frac{1}{2}$$</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>algebra</t>
+          <t>numeric</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>s1</t>
+          <t>s5</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>h1</t>
+          <t>h3</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -2220,43 +2332,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>problem</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Apply to denominator</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>What is $$\sin(4t)+\sin(2t)$$ as a product?</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>$$2\sin(3t)\cos(t)$$</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>algebra</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>s2</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
+          <t>Proving an Identity</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>https://openstax.org/books/precalculus-2e/pages/7-4-sum-to-product-and-product-to-sum-formulas</t>
+        </is>
+      </c>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
@@ -2270,30 +2366,26 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>step</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Simplify the fraction</t>
+          <t>Evaluate the expression: $$\frac{cos(4t)−cos(2t)}{sin(4t)+sin(2t)}$$</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Substitute the product forms back into the original fraction and simplify.</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
+          <t>$$-tant$$</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>algebraic</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
@@ -2312,39 +2404,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Simplify the expression</t>
+          <t>Apply sum-to-product formulas</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Simplify the expression $$\frac{-2\sin(3t)\sin(t)}{2\sin(3t)\cos(t)}$$.</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>$$-\frac{\sin(t)}{\cos(t)}$$</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>algebra</t>
-        </is>
-      </c>
+          <t>Use the sum-to-product formulas for the numerator and the denominator.</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>s3</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
+          <t>h1</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
@@ -2362,31 +2442,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Use a fundamental identity</t>
+          <t>Numerator formula</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Recall the definition of the tangent function.</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
+          <t>What is the sum-to-product formula for $$cos(A)−cos(B)$$?</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>$$−2sin\left(\frac{A+B}{2}\right)sin\left(\frac{A−B}{2}\right)$$</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>h3</t>
+          <t>algebraic</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>h2</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
@@ -2409,32 +2497,32 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Final simplification</t>
+          <t>Denominator formula</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>What is $$-\frac{\sin(t)}{\cos(t)}$$ in terms of tangent?</t>
+          <t>What is the sum-to-product formula for $$sin(A)+sin(B)$$?</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>$$-tant$$</t>
+          <t>$$2sin\left(\frac{A+B}{2}\right)cos\left(\frac{A−B}{2}\right)$$</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>algebra</t>
+          <t>algebraic</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>s4</t>
+          <t>s2</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>h3</t>
+          <t>h1</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -2449,31 +2537,39 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>sumprod7</t>
+          <t>sumprod6</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>problem</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Verifying the Identity Using Double-Angle Formulas and Reciprocal Identities</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>Apply formulas to numerator</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>For the numerator $$cos(4t)−cos(2t)$$, identify A and B and apply the formula.</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>https://openstax.org/books/precalculus-2e/pages/7-4-sum-to-product-and-product-to-sum-formulas</t>
-        </is>
-      </c>
+      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
@@ -2483,23 +2579,27 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>sumprod7</t>
+          <t>sumprod6</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>step</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Simplify the expression $$csc^{2}θ−2$$.</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>Numerator expression</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>What is $$cos(4t)−cos(2t)$$ expressed as a product?</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>$$\frac{cos(2θ)}{sin^{2}θ}$$</t>
+          <t>$$−2sin(3t)sin(t)$$</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2507,8 +2607,16 @@
           <t>algebraic</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>s3</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
@@ -2521,7 +2629,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>sumprod7</t>
+          <t>sumprod6</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2531,22 +2639,26 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Rewrite csc^2(theta)</t>
+          <t>Apply formulas to denominator</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Recall the reciprocal identity for cosecant: $$cscθ = \frac{1}{sinθ}$$</t>
+          <t>For the denominator $$sin(4t)+sin(2t)$$, identify A and B and apply the formula.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
+          <t>h3</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
           <t>h1</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
@@ -2559,7 +2671,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>sumprod7</t>
+          <t>sumprod6</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2569,17 +2681,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Rewrite $$csc^{2}θ$$</t>
+          <t>Denominator expression</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>What is $$csc^{2}θ$$ in terms of $$sin^{2}θ$$?</t>
+          <t>What is $$sin(4t)+sin(2t)$$ expressed as a product?</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>$$\frac{1}{sin^{2}θ}$$</t>
+          <t>$$2sin(3t)cos(t)$$</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2589,12 +2701,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>s1</t>
+          <t>s4</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>h1</t>
+          <t>h3</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -2609,7 +2721,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>sumprod7</t>
+          <t>sumprod6</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2619,24 +2731,24 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Combine terms</t>
+          <t>Simplify the fraction</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>After rewriting, combine the terms into a single fraction.</t>
+          <t>Substitute the product forms back into the original fraction and simplify.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>h2</t>
+          <t>h4</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>h1</t>
+          <t>h3</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -2651,7 +2763,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>sumprod7</t>
+          <t>sumprod6</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2661,17 +2773,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Combine into a single fraction</t>
+          <t>Final simplification</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Combine $$\frac{1}{sin^{2}θ} - 2$$ into a single fraction.</t>
+          <t>Simplify the expression $$\frac{−2sin(3t)sin(t)}{2sin(3t)cos(t)}$$.</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>$$\frac{1 - 2sin^{2}θ}{sin^{2}θ}$$</t>
+          <t>$$−tant$$</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2681,12 +2793,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>s2</t>
+          <t>s5</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>h2</t>
+          <t>h4</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -2706,35 +2818,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>problem</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Apply double-angle identity</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Recall the double-angle identity for cosine: $$cos(2θ) = 1 - 2sin^{2}θ$$.</t>
-        </is>
-      </c>
+          <t>Verifying the Identity Using Double-Angle Formulas and Reciprocal Identities</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>https://openstax.org/books/precalculus-2e/pages/7-4-sum-to-product-and-product-to-sum-formulas</t>
+        </is>
+      </c>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
@@ -2748,22 +2852,18 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>step</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Substitute double-angle identity</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>What is $$1 - 2sin^{2}θ$$ equivalent to using a double-angle identity?</t>
-        </is>
-      </c>
+          <t>Simplify the expression $$\frac{cos(2θ)}{sin^{2}θ}$$</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>$$cos(2θ)$$</t>
+          <t>$$csc^{2}θ−2$$</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2771,16 +2871,8 @@
           <t>algebraic</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>s3</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
@@ -2791,13 +2883,33 @@
       <c r="P57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr"/>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>sumprod7</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>hint</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Apply a double-angle identity</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>The expression contains $$cos(2θ)$$. Recall the double-angle identities for cosine: $$cos(2θ) = cos^2θ - sin^2θ$$, $$cos(2θ) = 1 - 2sin^2θ$$, or $$cos(2θ) = 2cos^2θ - 1$$.</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
@@ -2808,6 +2920,244 @@
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>sumprod7</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>scaffold</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Choose the appropriate identity</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Which form of the double-angle identity for $$cos(2θ)$$ would be most helpful when the denominator is $$sin^{2}θ$$?</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>$$1 - 2sin^2θ$$</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>mc</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>$$cos^2θ - sin^2θ$$|$$1 - 2sin^2θ$$|$$2cos^2θ - 1$$</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>sumprod7</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>hint</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Substitute and simplify</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Substitute the chosen identity for $$cos(2θ)$$ into the expression.</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>sumprod7</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>scaffold</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Perform the substitution</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>After substituting $$1 - 2sin^2θ$$ for $$cos(2θ)$$, what is the expression?</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>$$\frac{1 - 2sin^2θ}{sin^{2}θ}$$</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>algebraic</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>s2</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>sumprod7</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>hint</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Split the fraction</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>To simplify further, split the fraction into two terms and use reciprocal identities.</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>h3</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>sumprod7</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>scaffold</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Simplify the terms</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Simplify the expression $$\frac{1}{sin^{2}θ} - \frac{2sin^2θ}{sin^{2}θ}$$ to its final form.</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>$$csc^{2}θ−2$$</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>algebraic</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>s3</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>h3</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
